--- a/proje_sonuclari.xlsx
+++ b/proje_sonuclari.xlsx
@@ -457,10 +457,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.928802867264632</v>
+        <v>11.21772923752798</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3867373466491699</v>
+        <v>0.8073325157165527</v>
       </c>
       <c r="D2" t="n">
         <v>3</v>
@@ -473,13 +473,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.59924925092812</v>
+        <v>11.37310325548616</v>
       </c>
       <c r="C3" t="n">
-        <v>0.06021285057067871</v>
+        <v>0.1022250652313232</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -489,13 +489,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.38386492004284</v>
+        <v>11.60033191246425</v>
       </c>
       <c r="C4" t="n">
-        <v>0.06235909461975098</v>
+        <v>0.1328246593475342</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -505,10 +505,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.866333396104058</v>
+        <v>5.649571124115887</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03903651237487793</v>
+        <v>0.08639025688171387</v>
       </c>
       <c r="D5" t="n">
         <v>3</v>
